--- a/T388_Excel.xlsx
+++ b/T388_Excel.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D3DCB0-3088-46CA-B55D-1F93149D8A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA14EC6E-607E-4AA4-82F7-B5196FBEE5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{97914E35-3EC5-46A0-9D29-D522FBEA4F09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{97914E35-3EC5-46A0-9D29-D522FBEA4F09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="grade">Sheet1!$AD$2:$AD$7</definedName>
+    <definedName name="marks">Sheet1!$AB$2:$AB$7</definedName>
+    <definedName name="student_name">Sheet1!$Z$2:$Z$7</definedName>
+    <definedName name="subjects">Sheet1!$AA$2:$AA$7</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="99">
   <si>
     <t>ID</t>
   </si>
@@ -184,13 +190,160 @@
   </si>
   <si>
     <t>F21</t>
+  </si>
+  <si>
+    <t>Row Label 2</t>
+  </si>
+  <si>
+    <t>Row Label 1</t>
+  </si>
+  <si>
+    <t>student name</t>
+  </si>
+  <si>
+    <t>subjects</t>
+  </si>
+  <si>
+    <t>marks</t>
+  </si>
+  <si>
+    <t>roy</t>
+  </si>
+  <si>
+    <t>tom</t>
+  </si>
+  <si>
+    <t>smith</t>
+  </si>
+  <si>
+    <t>stokes</t>
+  </si>
+  <si>
+    <t>aman</t>
+  </si>
+  <si>
+    <t>amit</t>
+  </si>
+  <si>
+    <t>maths</t>
+  </si>
+  <si>
+    <t>science</t>
+  </si>
+  <si>
+    <t>english</t>
+  </si>
+  <si>
+    <t>eco</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>st. gmails</t>
+  </si>
+  <si>
+    <t>roy.@gmail.com</t>
+  </si>
+  <si>
+    <t>tom.@gmail.com</t>
+  </si>
+  <si>
+    <t>smith.@gmail.com</t>
+  </si>
+  <si>
+    <t>stokes.@gmail.com</t>
+  </si>
+  <si>
+    <t>aman.@gmail.com</t>
+  </si>
+  <si>
+    <t>amit.@gmail.com</t>
+  </si>
+  <si>
+    <t>IFERROR</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>LAYS</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>alpabetical</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>apple</t>
+  </si>
+  <si>
+    <t>ball</t>
+  </si>
+  <si>
+    <t>close</t>
+  </si>
+  <si>
+    <t>door</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>fox</t>
+  </si>
+  <si>
+    <t>grapes</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>ice cream</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,8 +410,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u val="double"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -277,8 +466,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -312,12 +512,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -354,12 +580,152 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="10" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="10" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Good" xfId="3" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -370,6 +736,1338 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:stockChart>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$AA$18:$AB$26</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="9"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>apple</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>ball</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>close</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>door</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>eng</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>fox</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>grapes</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>high</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>ice cream</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>a</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>b</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>c</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>d</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>e</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>f</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>g</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>h</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>i</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AC$18:$AC$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0786-4838-B760-72202FBC3B73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$AA$18:$AB$26</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="9"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>apple</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>ball</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>close</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>door</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>eng</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>fox</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>grapes</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>high</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>ice cream</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>a</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>b</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>c</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>d</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>e</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>f</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>g</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>h</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>i</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AD$18:$AD$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0786-4838-B760-72202FBC3B73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent3">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet1!$AA$18:$AB$26</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="9"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>apple</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>ball</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>close</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>door</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>eng</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>fox</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>grapes</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>high</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>ice cream</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>a</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>b</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>c</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>d</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>e</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>f</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>g</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>h</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>i</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AE$18:$AE$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>259</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>88.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>707</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>406</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1010</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>79</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0786-4838-B760-72202FBC3B73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:axId val="311413087"/>
+        <c:axId val="318234895"/>
+      </c:stockChart>
+      <c:catAx>
+        <c:axId val="311413087"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="318234895"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="318234895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="311413087"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="328">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="95000"/>
+              <a:lumOff val="5000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>408877</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>138461</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>86730</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>171295</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44CF2DEC-7385-CE24-5372-FCACF06135DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA34032B-CEBD-43E2-8E97-EC2349B84BF0}" name="Table1" displayName="Table1" ref="Z1:AG7" totalsRowShown="0" dataDxfId="14" dataCellStyle="Good">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{75D5843A-92D7-4D7B-8FD6-09296D6046B0}" name="student name" dataDxfId="13" dataCellStyle="Good"/>
+    <tableColumn id="2" xr3:uid="{EE511977-0428-4DD2-8775-7DBAAE1011AE}" name="subjects" dataDxfId="12" dataCellStyle="Good"/>
+    <tableColumn id="3" xr3:uid="{A43B78CD-D401-46D5-9052-B0DE2AC28839}" name="marks" dataDxfId="11" dataCellStyle="Percent"/>
+    <tableColumn id="7" xr3:uid="{5E40BC67-44B0-4E8F-BC6E-3779079E9B1A}" name="Column1" dataDxfId="6" dataCellStyle="Good"/>
+    <tableColumn id="4" xr3:uid="{81699359-3550-44BD-97F0-64EFCC7B9BD3}" name="grade" dataDxfId="10" dataCellStyle="Good">
+      <calculatedColumnFormula>IF(marks&gt;=95,"A+","B")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{9248B241-ABE0-477F-BC69-F49F32AF36EF}" name="st. gmails" dataDxfId="9" dataCellStyle="Good"/>
+    <tableColumn id="6" xr3:uid="{E8657F88-D910-4AC8-822C-C8273F8107F6}" name="IFERROR" dataDxfId="8" dataCellStyle="Good">
+      <calculatedColumnFormula>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{863D5A83-A32E-46F6-A6CA-393A8BDB04D6}" name="Column2" dataDxfId="7" dataCellStyle="Good">
+      <calculatedColumnFormula>LEN(Table1[[#This Row],[st. gmails]])</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{81D09F43-332C-4068-8720-15D43D980A45}" name="Table8" displayName="Table8" ref="AA17:AE26" totalsRowShown="0" dataDxfId="3">
+  <autoFilter ref="AA17:AE26" xr:uid="{81D09F43-332C-4068-8720-15D43D980A45}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{ECB24561-8FC2-46FC-ADB4-CDB2B1245BF3}" name="alpabetical" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{BF61F83D-8592-4E08-8EDD-5FDF02CF64C1}" name="name" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{BFBE6450-1CF9-43A9-AED0-14C4A73F7154}" name="rank" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{A96F1296-0B29-4376-8C86-86B54DE8545B}" name="value" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{680433EC-2048-4C8A-BCB1-EDB4E05049E1}" name="Column1" dataDxfId="0">
+      <calculatedColumnFormula>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -669,20 +2367,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC74FB1-AD57-4850-AA87-E06A6A7A96BD}">
-  <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AH32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" customWidth="1"/>
+    <col min="27" max="27" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="10.85546875" customWidth="1"/>
+    <col min="30" max="30" width="10.42578125" customWidth="1"/>
+    <col min="31" max="31" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -710,29 +2414,53 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="14" t="s">
         <v>38</v>
       </c>
       <c r="W1" s="11">
         <v>23</v>
       </c>
+      <c r="Z1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -762,29 +2490,56 @@
       <c r="J2" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="Q2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="5">
         <v>40</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="5">
         <v>2</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="5">
         <v>80</v>
       </c>
       <c r="W2" s="11">
         <v>24</v>
       </c>
+      <c r="Z2" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA2" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB2" s="20">
+        <v>88</v>
+      </c>
+      <c r="AC2" s="19">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="19" t="str">
+        <f>IF(marks&gt;=95,"A+","B")</f>
+        <v>B</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF2" s="19">
+        <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
+        <v>11</v>
+      </c>
+      <c r="AG2" s="19">
+        <f>LEN(Table1[[#This Row],[st. gmails]])</f>
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -814,22 +2569,22 @@
       <c r="J3" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="R3" s="11">
+      <c r="R3" s="5">
         <v>120</v>
       </c>
-      <c r="S3" s="11">
+      <c r="S3" s="5">
         <v>2</v>
       </c>
-      <c r="T3" s="11">
+      <c r="T3" s="5">
         <v>240</v>
       </c>
       <c r="W3" s="11" t="b">
@@ -839,8 +2594,35 @@
         <f>COUNTA(W1:W6)</f>
         <v>6</v>
       </c>
+      <c r="Z3" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB3" s="20">
+        <v>75</v>
+      </c>
+      <c r="AC3" s="19">
+        <v>6</v>
+      </c>
+      <c r="AD3" s="19" t="str">
+        <f>IF(marks&gt;=95,"A+","B")</f>
+        <v>B</v>
+      </c>
+      <c r="AE3" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF3" s="21">
+        <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
+        <v>12.5</v>
+      </c>
+      <c r="AG3" s="19">
+        <f>LEN(Table1[[#This Row],[st. gmails]])</f>
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -870,22 +2652,22 @@
       <c r="J4" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="R4" s="11">
+      <c r="R4" s="5">
         <v>60</v>
       </c>
-      <c r="S4" s="11">
+      <c r="S4" s="5">
         <v>4</v>
       </c>
-      <c r="T4" s="11">
+      <c r="T4" s="5">
         <v>240</v>
       </c>
       <c r="W4" s="11">
@@ -895,8 +2677,35 @@
         <f>COUNTBLANK(W1:W6)</f>
         <v>0</v>
       </c>
+      <c r="Z4" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA4" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB4" s="20">
+        <v>80</v>
+      </c>
+      <c r="AC4" s="19">
+        <v>55</v>
+      </c>
+      <c r="AD4" s="19" t="str">
+        <f>IF(marks&gt;=95,"A+","B")</f>
+        <v>B</v>
+      </c>
+      <c r="AE4" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF4" s="21">
+        <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
+        <v>1.4545454545454546</v>
+      </c>
+      <c r="AG4" s="19">
+        <f>LEN(Table1[[#This Row],[st. gmails]])</f>
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -926,29 +2735,56 @@
       <c r="J5" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="P5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="Q5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="5">
         <v>100</v>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="5">
         <v>3</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="5">
         <v>300</v>
       </c>
       <c r="W5" s="11" t="s">
         <v>49</v>
       </c>
+      <c r="Z5" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA5" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB5" s="20">
+        <v>93</v>
+      </c>
+      <c r="AC5" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="19" t="str">
+        <f>IF(marks&gt;=95,"A+","B")</f>
+        <v>B</v>
+      </c>
+      <c r="AE5" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF5" s="19" t="str">
+        <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
+        <v>False</v>
+      </c>
+      <c r="AG5" s="19">
+        <f>LEN(Table1[[#This Row],[st. gmails]])</f>
+        <v>17</v>
+      </c>
     </row>
-    <row r="6" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -978,53 +2814,107 @@
       <c r="J6" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="P6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="Q6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="5">
         <v>120</v>
       </c>
-      <c r="S6" s="11">
+      <c r="S6" s="5">
         <v>6</v>
       </c>
-      <c r="T6" s="11">
+      <c r="T6" s="5">
         <v>720</v>
       </c>
       <c r="W6" s="11">
         <v>30</v>
       </c>
+      <c r="Z6" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB6" s="20">
+        <v>99</v>
+      </c>
+      <c r="AC6" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD6" s="19" t="str">
+        <f>IF(marks&gt;=95,"A+","B")</f>
+        <v>A+</v>
+      </c>
+      <c r="AE6" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF6" s="19" t="str">
+        <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
+        <v>False</v>
+      </c>
+      <c r="AG6" s="19">
+        <f>LEN(Table1[[#This Row],[st. gmails]])</f>
+        <v>15</v>
+      </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="P7" s="11" t="s">
+      <c r="P7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="5">
         <v>25</v>
       </c>
-      <c r="S7" s="11">
+      <c r="S7" s="5">
         <v>2</v>
       </c>
-      <c r="T7" s="11">
+      <c r="T7" s="5">
         <v>50</v>
       </c>
+      <c r="Z7" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA7" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB7" s="20">
+        <v>95</v>
+      </c>
+      <c r="AC7" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="19" t="str">
+        <f>IF(marks&gt;=95,"A+","B")</f>
+        <v>A+</v>
+      </c>
+      <c r="AE7" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF7" s="19" t="str">
+        <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
+        <v>False</v>
+      </c>
+      <c r="AG7" s="19">
+        <f>LEN(Table1[[#This Row],[st. gmails]])</f>
+        <v>15</v>
+      </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
@@ -1040,7 +2930,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="3" t="s">
@@ -1066,8 +2956,14 @@
         <f>SUMIF(Q2:Q7,"Fruit",S2:S7)</f>
         <v>10</v>
       </c>
+      <c r="AA9" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB9" s="17" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="3" t="s">
@@ -1090,8 +2986,15 @@
         <f>SUMIFS(S2:S7,P2:P7,"Frozen",Q2:Q7,"Fruit")</f>
         <v>8</v>
       </c>
+      <c r="AA10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB10">
+        <f>VLOOKUP(AA10,Table1[],3,0)</f>
+        <v>88</v>
+      </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3" t="s">
@@ -1110,8 +3013,11 @@
         <f>I9+I12</f>
         <v>600</v>
       </c>
+      <c r="AA11" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3" t="s">
@@ -1129,8 +3035,17 @@
       <c r="I12">
         <v>400</v>
       </c>
+      <c r="Q12" t="s">
+        <v>51</v>
+      </c>
+      <c r="R12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="8" t="s">
@@ -1145,8 +3060,14 @@
       <c r="G13" s="11">
         <v>208.1</v>
       </c>
+      <c r="Q13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F14" s="12">
         <v>46174</v>
       </c>
@@ -1157,33 +3078,182 @@
         <f>I9*5</f>
         <v>1000</v>
       </c>
+      <c r="Q14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="X14" s="16" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="F15" s="12">
         <v>46204</v>
       </c>
       <c r="G15" s="11">
         <v>208.2</v>
       </c>
+      <c r="Q15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="K16">
         <f>I12*6</f>
         <v>2400</v>
       </c>
+      <c r="Q16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="I17">
         <v>1000</v>
       </c>
+      <c r="Q17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q18" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA18" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB18" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC18" s="22">
+        <v>9</v>
+      </c>
+      <c r="AD18" s="22">
+        <v>250</v>
+      </c>
+      <c r="AE18" s="22">
+        <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AA19" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB19" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC19" s="22">
+        <v>7</v>
+      </c>
+      <c r="AD19" s="22">
+        <v>50</v>
+      </c>
+      <c r="AE19" s="22">
+        <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="K20">
         <f>I17+55</f>
         <v>1055</v>
       </c>
+      <c r="Q20" t="s">
+        <v>42</v>
+      </c>
+      <c r="R20" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA20" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB20" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC20" s="22">
+        <v>8.5</v>
+      </c>
+      <c r="AD20" s="22">
+        <v>80</v>
+      </c>
+      <c r="AE20" s="22">
+        <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
+        <v>88.5</v>
+      </c>
+      <c r="AH20" s="7"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AA21" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB21" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC21" s="22">
+        <v>7</v>
+      </c>
+      <c r="AD21" s="22">
+        <v>700</v>
+      </c>
+      <c r="AE21" s="22">
+        <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
+        <v>707</v>
+      </c>
+      <c r="AH21" s="7"/>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q22">
+        <f>SUMIFS(T2:T7,Q13:Q18,Q20,P2:P7,R20)</f>
+        <v>300</v>
+      </c>
+      <c r="AA22" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB22" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC22" s="22">
+        <v>4</v>
+      </c>
+      <c r="AD22" s="22">
+        <v>100</v>
+      </c>
+      <c r="AE22" s="22">
+        <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
+        <v>104</v>
+      </c>
+      <c r="AH22" s="7"/>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>33</v>
       </c>
@@ -1202,8 +3272,25 @@
       <c r="F23" s="13" t="s">
         <v>38</v>
       </c>
+      <c r="AA23" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB23" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC23" s="22">
+        <v>6</v>
+      </c>
+      <c r="AD23" s="22">
+        <v>400</v>
+      </c>
+      <c r="AE23" s="22">
+        <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
+        <v>406</v>
+      </c>
+      <c r="AH23" s="7"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>39</v>
       </c>
@@ -1222,8 +3309,25 @@
       <c r="F24" s="11">
         <v>80</v>
       </c>
+      <c r="AA24" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB24" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC24" s="22">
+        <v>10</v>
+      </c>
+      <c r="AD24" s="22">
+        <v>1000</v>
+      </c>
+      <c r="AE24" s="22">
+        <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
+        <v>1010</v>
+      </c>
+      <c r="AH24" s="7"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>40</v>
       </c>
@@ -1245,8 +3349,25 @@
       <c r="J25">
         <v>200</v>
       </c>
+      <c r="AA25" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB25" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC25" s="22">
+        <v>6</v>
+      </c>
+      <c r="AD25" s="22">
+        <v>50</v>
+      </c>
+      <c r="AE25" s="22">
+        <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
+        <v>56</v>
+      </c>
+      <c r="AH25" s="7"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>41</v>
       </c>
@@ -1269,8 +3390,24 @@
         <f>J25+J27</f>
         <v>500</v>
       </c>
+      <c r="AA26" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB26" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC26" s="22">
+        <v>9</v>
+      </c>
+      <c r="AD26" s="22">
+        <v>70</v>
+      </c>
+      <c r="AE26" s="22">
+        <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
+        <v>79</v>
+      </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>42</v>
       </c>
@@ -1293,7 +3430,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>43</v>
       </c>
@@ -1313,7 +3450,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>44</v>
       </c>
@@ -1333,7 +3470,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -1341,7 +3478,7 @@
       <c r="E30" s="13"/>
       <c r="F30" s="13"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -1349,7 +3486,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1360,7 +3497,7 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D8:D13">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1373,15 +3510,60 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AB27:AC1048576 AB1:AC8 AB10:AC14 AC9">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D112B2C1-F653-4E25-A221-59F742710B7E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE18:AE26">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="5Rating">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="20"/>
+        <cfvo type="percent" val="40"/>
+        <cfvo type="percent" val="60"/>
+        <cfvo type="percent" val="80"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q20" xr:uid="{179EE944-FFB1-4A7D-8AAA-099D5A8C61C5}">
+      <formula1>$O$2:$O$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R13:R18 R20" xr:uid="{994FC5CE-974B-47DC-B8AC-D273DD4BE681}">
+      <formula1>$P$2:$P$7</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{8CDFE076-B84D-47F7-81DC-EBE01424DE7D}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{37DF5225-85FB-4F03-81A8-4A159C453842}"/>
     <hyperlink ref="G4" r:id="rId3" xr:uid="{450BF1C8-AF3C-42FA-A402-88E9E5A8AD6E}"/>
     <hyperlink ref="G5" r:id="rId4" xr:uid="{D09DE00B-C751-41DE-9407-23E1A969194B}"/>
     <hyperlink ref="G6" r:id="rId5" xr:uid="{CE0B6BFB-416D-4DC4-89A9-32AEA3FCD8B9}"/>
+    <hyperlink ref="AE2" r:id="rId6" xr:uid="{8BCC57DF-F199-48BD-B9B2-36A163AC2B7E}"/>
+    <hyperlink ref="AE3" r:id="rId7" xr:uid="{C363DF98-B913-4F52-8D61-E4E2CEE8989F}"/>
+    <hyperlink ref="AE4" r:id="rId8" xr:uid="{D6B9E294-D4A0-4D86-BF3C-EB5812A8A18A}"/>
+    <hyperlink ref="AE5" r:id="rId9" xr:uid="{5E3054B8-9D43-4564-810F-75FDBE0DDE5C}"/>
+    <hyperlink ref="AE6" r:id="rId10" xr:uid="{20AB87D2-6B90-4AE2-92AD-B1505A6C243F}"/>
+    <hyperlink ref="AE7" r:id="rId11" xr:uid="{BA487083-1955-4B5F-A7AA-75CA81171D32}"/>
+    <hyperlink ref="X14" r:id="rId12" xr:uid="{257603B7-9B4A-4504-83A8-73CCA40D8EE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
+  <drawing r:id="rId14"/>
+  <tableParts count="2">
+    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
+  </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -1398,6 +3580,19 @@
           </x14:cfRule>
           <xm:sqref>D8:D13</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D112B2C1-F653-4E25-A221-59F742710B7E}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF008AEF"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AB27:AC1048576 AB1:AC8 AB10:AC14 AC9</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/T388_Excel.xlsx
+++ b/T388_Excel.xlsx
@@ -8,18 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA14EC6E-607E-4AA4-82F7-B5196FBEE5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29252722-4DFC-42DC-A4D1-2F877DC160CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{97914E35-3EC5-46A0-9D29-D522FBEA4F09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97914E35-3EC5-46A0-9D29-D522FBEA4F09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="grade">Sheet1!$AD$2:$AD$7</definedName>
-    <definedName name="marks">Sheet1!$AB$2:$AB$7</definedName>
-    <definedName name="student_name">Sheet1!$Z$2:$Z$7</definedName>
-    <definedName name="subjects">Sheet1!$AA$2:$AA$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$O$4:$T$10</definedName>
+    <definedName name="chemistry">Sheet2!$E$2:$E$8</definedName>
+    <definedName name="english">Sheet2!$D$2:$D$8</definedName>
+    <definedName name="grade">Sheet1!$AD$5:$AD$10</definedName>
+    <definedName name="marks">Sheet1!$AB$5:$AB$10</definedName>
+    <definedName name="maths">Sheet2!$B$2:$B$8</definedName>
+    <definedName name="science">Sheet2!$C$2:$C$8</definedName>
+    <definedName name="student_name" localSheetId="1">Sheet2!$A$2:$A$8</definedName>
+    <definedName name="student_name">Sheet1!$Z$5:$Z$10</definedName>
+    <definedName name="subjects">Sheet1!$AA$5:$AA$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="116">
   <si>
     <t>ID</t>
   </si>
@@ -337,13 +348,64 @@
   </si>
   <si>
     <t>ice cream</t>
+  </si>
+  <si>
+    <t>Sujal's Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maths </t>
+  </si>
+  <si>
+    <t>chemistry</t>
+  </si>
+  <si>
+    <t>ajit</t>
+  </si>
+  <si>
+    <t>amay</t>
+  </si>
+  <si>
+    <t>raj</t>
+  </si>
+  <si>
+    <t>sam</t>
+  </si>
+  <si>
+    <t>roman</t>
+  </si>
+  <si>
+    <t>gmails</t>
+  </si>
+  <si>
+    <t>roy.101@gmail.com</t>
+  </si>
+  <si>
+    <t>ajit.101@gmail.com</t>
+  </si>
+  <si>
+    <t>amay.101@gmail.com</t>
+  </si>
+  <si>
+    <t>raj.101@gmail.com</t>
+  </si>
+  <si>
+    <t>sam.101@gmail.com</t>
+  </si>
+  <si>
+    <t>tom.101@gmail.com</t>
+  </si>
+  <si>
+    <t>roman.101@gmail.com</t>
+  </si>
+  <si>
+    <t>percentage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,6 +508,13 @@
       <name val="Calibri Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -478,7 +547,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -536,6 +605,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -543,7 +708,7 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -568,13 +733,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -583,8 +742,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -598,6 +757,58 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -605,7 +816,57 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -639,7 +900,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -670,6 +930,7 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -724,6 +985,149 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -795,6 +1199,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AC$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>rank</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -813,7 +1228,7 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$AA$18:$AB$26</c:f>
+              <c:f>Sheet1!$AA$21:$AB$29</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="9"/>
                 <c:lvl>
@@ -879,7 +1294,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AC$18:$AC$26</c:f>
+              <c:f>Sheet1!$AC$21:$AC$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -923,6 +1338,17 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AD$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>value</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -941,7 +1367,7 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$AA$18:$AB$26</c:f>
+              <c:f>Sheet1!$AA$21:$AB$29</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="9"/>
                 <c:lvl>
@@ -1007,7 +1433,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AD$18:$AD$26</c:f>
+              <c:f>Sheet1!$AD$21:$AD$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1051,6 +1477,17 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AE$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Column1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="25400" cap="rnd">
               <a:noFill/>
@@ -1111,7 +1548,7 @@
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Sheet1!$AA$18:$AB$26</c:f>
+              <c:f>Sheet1!$AA$21:$AB$29</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="9"/>
                 <c:lvl>
@@ -1177,7 +1614,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AE$18:$AE$26</c:f>
+              <c:f>Sheet1!$AE$21:$AE$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1438,7 +1875,520 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$R$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>UNIT PRICE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$R$5:$R$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>120</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-987A-4CC0-89C3-E9645DC77023}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$S$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>QTY.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="75000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$S$5:$S$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-987A-4CC0-89C3-E9645DC77023}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="315"/>
+        <c:overlap val="-40"/>
+        <c:axId val="959398224"/>
+        <c:axId val="855429968"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="959398224"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="855429968"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="855429968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="959398224"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1991,19 +2941,568 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="213">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>408877</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>138461</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
       <xdr:colOff>86730</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>171295</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2029,24 +3528,60 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>92927</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>7745</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>7740</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4A4E1A3-0A3D-FF68-D09E-14BBA16CF965}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA34032B-CEBD-43E2-8E97-EC2349B84BF0}" name="Table1" displayName="Table1" ref="Z1:AG7" totalsRowShown="0" dataDxfId="14" dataCellStyle="Good">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA34032B-CEBD-43E2-8E97-EC2349B84BF0}" name="Table1" displayName="Table1" ref="Z4:AG10" totalsRowShown="0" dataDxfId="16" dataCellStyle="Good">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{75D5843A-92D7-4D7B-8FD6-09296D6046B0}" name="student name" dataDxfId="13" dataCellStyle="Good"/>
-    <tableColumn id="2" xr3:uid="{EE511977-0428-4DD2-8775-7DBAAE1011AE}" name="subjects" dataDxfId="12" dataCellStyle="Good"/>
-    <tableColumn id="3" xr3:uid="{A43B78CD-D401-46D5-9052-B0DE2AC28839}" name="marks" dataDxfId="11" dataCellStyle="Percent"/>
-    <tableColumn id="7" xr3:uid="{5E40BC67-44B0-4E8F-BC6E-3779079E9B1A}" name="Column1" dataDxfId="6" dataCellStyle="Good"/>
-    <tableColumn id="4" xr3:uid="{81699359-3550-44BD-97F0-64EFCC7B9BD3}" name="grade" dataDxfId="10" dataCellStyle="Good">
+    <tableColumn id="1" xr3:uid="{75D5843A-92D7-4D7B-8FD6-09296D6046B0}" name="student name" dataDxfId="15" dataCellStyle="Good"/>
+    <tableColumn id="2" xr3:uid="{EE511977-0428-4DD2-8775-7DBAAE1011AE}" name="subjects" dataDxfId="14" dataCellStyle="Good"/>
+    <tableColumn id="3" xr3:uid="{A43B78CD-D401-46D5-9052-B0DE2AC28839}" name="marks" dataDxfId="13" dataCellStyle="Percent"/>
+    <tableColumn id="7" xr3:uid="{5E40BC67-44B0-4E8F-BC6E-3779079E9B1A}" name="Column1" dataDxfId="12" dataCellStyle="Good"/>
+    <tableColumn id="4" xr3:uid="{81699359-3550-44BD-97F0-64EFCC7B9BD3}" name="grade" dataDxfId="11" dataCellStyle="Good">
       <calculatedColumnFormula>IF(marks&gt;=95,"A+","B")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9248B241-ABE0-477F-BC69-F49F32AF36EF}" name="st. gmails" dataDxfId="9" dataCellStyle="Good"/>
-    <tableColumn id="6" xr3:uid="{E8657F88-D910-4AC8-822C-C8273F8107F6}" name="IFERROR" dataDxfId="8" dataCellStyle="Good">
+    <tableColumn id="5" xr3:uid="{9248B241-ABE0-477F-BC69-F49F32AF36EF}" name="st. gmails" dataDxfId="10" dataCellStyle="Good"/>
+    <tableColumn id="6" xr3:uid="{E8657F88-D910-4AC8-822C-C8273F8107F6}" name="IFERROR" dataDxfId="9" dataCellStyle="Good">
       <calculatedColumnFormula>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{863D5A83-A32E-46F6-A6CA-393A8BDB04D6}" name="Column2" dataDxfId="7" dataCellStyle="Good">
+    <tableColumn id="8" xr3:uid="{863D5A83-A32E-46F6-A6CA-393A8BDB04D6}" name="Column2" dataDxfId="8" dataCellStyle="Good">
       <calculatedColumnFormula>LEN(Table1[[#This Row],[st. gmails]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2055,18 +3590,39 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{81D09F43-332C-4068-8720-15D43D980A45}" name="Table8" displayName="Table8" ref="AA17:AE26" totalsRowShown="0" dataDxfId="3">
-  <autoFilter ref="AA17:AE26" xr:uid="{81D09F43-332C-4068-8720-15D43D980A45}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{81D09F43-332C-4068-8720-15D43D980A45}" name="Table8" displayName="Table8" ref="AA20:AE29" totalsRowShown="0" dataDxfId="7">
+  <autoFilter ref="AA20:AE29" xr:uid="{81D09F43-332C-4068-8720-15D43D980A45}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{ECB24561-8FC2-46FC-ADB4-CDB2B1245BF3}" name="alpabetical" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{BF61F83D-8592-4E08-8EDD-5FDF02CF64C1}" name="name" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{BFBE6450-1CF9-43A9-AED0-14C4A73F7154}" name="rank" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{A96F1296-0B29-4376-8C86-86B54DE8545B}" name="value" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{680433EC-2048-4C8A-BCB1-EDB4E05049E1}" name="Column1" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{ECB24561-8FC2-46FC-ADB4-CDB2B1245BF3}" name="alpabetical" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{BF61F83D-8592-4E08-8EDD-5FDF02CF64C1}" name="name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{BFBE6450-1CF9-43A9-AED0-14C4A73F7154}" name="rank" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{A96F1296-0B29-4376-8C86-86B54DE8545B}" name="value" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{680433EC-2048-4C8A-BCB1-EDB4E05049E1}" name="Column1" dataDxfId="2">
       <calculatedColumnFormula>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F8682F26-C882-41EF-A41B-C0E33D339B32}" name="Table2" displayName="Table2" ref="A1:G8" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{B56283BB-AF07-4862-81B2-09DA638D3524}" name="student name" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{81138EB3-4928-4A83-AFFC-3724E1429286}" name="maths " dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{B0E8492E-BA53-4613-BA81-39F875867CC7}" name="science" dataDxfId="20">
+      <calculatedColumnFormula>RANDBETWEEN(50,66)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{11294772-02C9-4698-8910-CECDDD4C5683}" name="english" dataDxfId="19">
+      <calculatedColumnFormula>RANDBETWEEN(55,66)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{D506DEC0-F4D9-4AD3-8547-FD4909FE68B4}" name="chemistry" dataDxfId="18">
+      <calculatedColumnFormula>RANDBETWEEN(50,66)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{09B49C5B-04AA-4699-B923-8B9DA88B3F08}" name="gmails" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{CDA5F492-9EAD-4C5A-9739-84D88F8E03D0}" name="percentage" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2367,7 +3923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC74FB1-AD57-4850-AA87-E06A6A7A96BD}">
-  <dimension ref="A1:AH32"/>
+  <dimension ref="A2:AH35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -2386,1117 +3942,1047 @@
     <col min="31" max="31" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="2" spans="1:33" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q4" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="W1" s="11">
+      <c r="W4" s="10">
         <v>23</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z4" t="s">
         <v>52</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA4" t="s">
         <v>53</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB4" t="s">
         <v>54</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC4" t="s">
         <v>74</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD4" t="s">
         <v>65</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE4" t="s">
         <v>66</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF4" t="s">
         <v>73</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B5" s="3">
         <v>23</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D5" s="3">
         <v>23000</v>
       </c>
-      <c r="E2" s="5">
-        <f>D2*5%</f>
+      <c r="E5" s="5">
+        <f>D5*5%</f>
         <v>1150</v>
       </c>
-      <c r="F2" s="5">
-        <f>D2+E2</f>
+      <c r="F5" s="5">
+        <f>D5+E5</f>
         <v>24150</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J5" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R5" s="5">
         <v>40</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S5" s="5">
         <v>2</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T5" s="5">
         <v>80</v>
       </c>
-      <c r="W2" s="11">
+      <c r="W5" s="10">
         <v>24</v>
       </c>
-      <c r="Z2" s="19" t="s">
+      <c r="Z5" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="AA2" s="19" t="s">
+      <c r="AA5" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AB2" s="20">
+      <c r="AB5" s="18">
         <v>88</v>
       </c>
-      <c r="AC2" s="19">
+      <c r="AC5" s="17">
         <v>8</v>
       </c>
-      <c r="AD2" s="19" t="str">
-        <f>IF(marks&gt;=95,"A+","B")</f>
+      <c r="AD5" s="17" t="str">
+        <f t="shared" ref="AD5:AD10" si="0">IF(marks&gt;=95,"A+","B")</f>
         <v>B</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AE5" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="AF2" s="19">
+      <c r="AF5" s="17">
         <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
         <v>11</v>
       </c>
-      <c r="AG2" s="19">
+      <c r="AG5" s="17">
         <f>LEN(Table1[[#This Row],[st. gmails]])</f>
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B6" s="3">
         <v>25</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D6" s="3">
         <v>45000</v>
       </c>
-      <c r="E3" s="5">
-        <f t="shared" ref="E3:E6" si="0">D3*5%</f>
+      <c r="E6" s="5">
+        <f t="shared" ref="E6:E9" si="1">D6*5%</f>
         <v>2250</v>
       </c>
-      <c r="F3" s="5">
-        <f t="shared" ref="F3:F5" si="1">D3+E3</f>
+      <c r="F6" s="5">
+        <f t="shared" ref="F6:F8" si="2">D6+E6</f>
         <v>47250</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I6" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J6" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="R3" s="5">
+      <c r="R6" s="5">
         <v>120</v>
       </c>
-      <c r="S3" s="5">
+      <c r="S6" s="5">
         <v>2</v>
       </c>
-      <c r="T3" s="5">
+      <c r="T6" s="5">
         <v>240</v>
       </c>
-      <c r="W3" s="11" t="b">
+      <c r="W6" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="X3">
-        <f>COUNTA(W1:W6)</f>
+      <c r="X6">
+        <f>COUNTA(W4:W9)</f>
         <v>6</v>
       </c>
-      <c r="Z3" s="19" t="s">
+      <c r="Z6" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="AA3" s="19" t="s">
+      <c r="AA6" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="AB3" s="20">
+      <c r="AB6" s="18">
         <v>75</v>
       </c>
-      <c r="AC3" s="19">
+      <c r="AC6" s="17">
         <v>6</v>
       </c>
-      <c r="AD3" s="19" t="str">
-        <f>IF(marks&gt;=95,"A+","B")</f>
+      <c r="AD6" s="17" t="str">
+        <f t="shared" si="0"/>
         <v>B</v>
       </c>
-      <c r="AE3" s="19" t="s">
+      <c r="AE6" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="AF3" s="21">
+      <c r="AF6" s="19">
         <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
         <v>12.5</v>
       </c>
-      <c r="AG3" s="19">
+      <c r="AG6" s="17">
         <f>LEN(Table1[[#This Row],[st. gmails]])</f>
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B7" s="3">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D7" s="3">
         <v>46000</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E7" s="5">
+        <f t="shared" si="1"/>
+        <v>2300</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="2"/>
+        <v>48300</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" s="5">
+        <v>25</v>
+      </c>
+      <c r="S7" s="5">
+        <v>2</v>
+      </c>
+      <c r="T7" s="5">
+        <v>50</v>
+      </c>
+      <c r="W7" s="10">
+        <v>25</v>
+      </c>
+      <c r="X7">
+        <f>COUNTBLANK(W4:W9)</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA7" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB7" s="18">
+        <v>80</v>
+      </c>
+      <c r="AC7" s="17">
+        <v>55</v>
+      </c>
+      <c r="AD7" s="17" t="str">
         <f t="shared" si="0"/>
-        <v>2300</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="1"/>
-        <v>48300</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="R4" s="5">
-        <v>60</v>
-      </c>
-      <c r="S4" s="5">
-        <v>4</v>
-      </c>
-      <c r="T4" s="5">
-        <v>240</v>
-      </c>
-      <c r="W4" s="11">
-        <v>25</v>
-      </c>
-      <c r="X4">
-        <f>COUNTBLANK(W1:W6)</f>
-        <v>0</v>
-      </c>
-      <c r="Z4" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA4" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB4" s="20">
-        <v>80</v>
-      </c>
-      <c r="AC4" s="19">
-        <v>55</v>
-      </c>
-      <c r="AD4" s="19" t="str">
-        <f>IF(marks&gt;=95,"A+","B")</f>
         <v>B</v>
       </c>
-      <c r="AE4" s="19" t="s">
+      <c r="AE7" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="AF4" s="21">
+      <c r="AF7" s="19">
         <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
         <v>1.4545454545454546</v>
       </c>
-      <c r="AG4" s="19">
+      <c r="AG7" s="17">
         <f>LEN(Table1[[#This Row],[st. gmails]])</f>
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B8" s="3">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D8" s="3">
         <v>30000</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E8" s="5">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="2"/>
+        <v>31500</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R8" s="5">
+        <v>100</v>
+      </c>
+      <c r="S8" s="5">
+        <v>3</v>
+      </c>
+      <c r="T8" s="5">
+        <v>300</v>
+      </c>
+      <c r="W8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z8" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA8" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB8" s="18">
+        <v>93</v>
+      </c>
+      <c r="AC8" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="17" t="str">
         <f t="shared" si="0"/>
-        <v>1500</v>
-      </c>
-      <c r="F5" s="5">
-        <f t="shared" si="1"/>
-        <v>31500</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="R5" s="5">
-        <v>100</v>
-      </c>
-      <c r="S5" s="5">
-        <v>3</v>
-      </c>
-      <c r="T5" s="5">
-        <v>300</v>
-      </c>
-      <c r="W5" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z5" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA5" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB5" s="20">
-        <v>93</v>
-      </c>
-      <c r="AC5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="19" t="str">
-        <f>IF(marks&gt;=95,"A+","B")</f>
         <v>B</v>
       </c>
-      <c r="AE5" s="19" t="s">
+      <c r="AE8" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="AF5" s="19" t="str">
+      <c r="AF8" s="17" t="str">
         <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
         <v>False</v>
       </c>
-      <c r="AG5" s="19">
+      <c r="AG8" s="17">
         <f>LEN(Table1[[#This Row],[st. gmails]])</f>
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="9" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B9" s="3">
         <v>25</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D9" s="3">
         <v>25000</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E9" s="5">
+        <f t="shared" si="1"/>
+        <v>1250</v>
+      </c>
+      <c r="F9" s="6">
+        <f>D9+E9</f>
+        <v>26250</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="R9" s="5">
+        <v>60</v>
+      </c>
+      <c r="S9" s="5">
+        <v>4</v>
+      </c>
+      <c r="T9" s="5">
+        <v>240</v>
+      </c>
+      <c r="W9" s="10">
+        <v>30</v>
+      </c>
+      <c r="Z9" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA9" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB9" s="18">
+        <v>99</v>
+      </c>
+      <c r="AC9" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD9" s="17" t="str">
         <f t="shared" si="0"/>
-        <v>1250</v>
-      </c>
-      <c r="F6" s="6">
-        <f>D6+E6</f>
-        <v>26250</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="R6" s="5">
-        <v>120</v>
-      </c>
-      <c r="S6" s="5">
-        <v>6</v>
-      </c>
-      <c r="T6" s="5">
-        <v>720</v>
-      </c>
-      <c r="W6" s="11">
-        <v>30</v>
-      </c>
-      <c r="Z6" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA6" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB6" s="20">
-        <v>99</v>
-      </c>
-      <c r="AC6" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="AD6" s="19" t="str">
-        <f>IF(marks&gt;=95,"A+","B")</f>
         <v>A+</v>
       </c>
-      <c r="AE6" s="19" t="s">
+      <c r="AE9" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="AF6" s="19" t="str">
+      <c r="AF9" s="17" t="str">
         <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
         <v>False</v>
       </c>
-      <c r="AG6" s="19">
+      <c r="AG9" s="17">
         <f>LEN(Table1[[#This Row],[st. gmails]])</f>
         <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="O7" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="R7" s="5">
-        <v>25</v>
-      </c>
-      <c r="S7" s="5">
-        <v>2</v>
-      </c>
-      <c r="T7" s="5">
-        <v>50</v>
-      </c>
-      <c r="Z7" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA7" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB7" s="20">
-        <v>95</v>
-      </c>
-      <c r="AC7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="19" t="str">
-        <f>IF(marks&gt;=95,"A+","B")</f>
-        <v>A+</v>
-      </c>
-      <c r="AE7" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF7" s="19" t="str">
-        <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
-        <v>False</v>
-      </c>
-      <c r="AG7" s="19">
-        <f>LEN(Table1[[#This Row],[st. gmails]])</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="1">
-        <v>30</v>
-      </c>
-      <c r="F9" s="12">
-        <v>46023</v>
-      </c>
-      <c r="G9" s="11">
-        <v>205</v>
-      </c>
-      <c r="I9">
-        <v>200</v>
-      </c>
-      <c r="Q9">
-        <f>COUNTIF(Q2:Q7,"Fruit")</f>
-        <v>3</v>
-      </c>
-      <c r="R9">
-        <f>SUMIF(Q2:Q7,"Fruit",S2:S7)</f>
-        <v>10</v>
-      </c>
-      <c r="AA9" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB9" s="17" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="C10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="1">
-        <v>45</v>
-      </c>
-      <c r="F10" s="12">
-        <v>46054</v>
-      </c>
-      <c r="G10" s="11">
-        <v>206.7</v>
-      </c>
-      <c r="Q10">
-        <f>COUNTIFS(P2:P7,"Frozen",Q2:Q7,"vegetable")</f>
-        <v>2</v>
-      </c>
-      <c r="R10">
-        <f>SUMIFS(S2:S7,P2:P7,"Frozen",Q2:Q7,"Fruit")</f>
-        <v>8</v>
-      </c>
-      <c r="AA10" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB10">
-        <f>VLOOKUP(AA10,Table1[],3,0)</f>
-        <v>88</v>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="O10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="R10" s="5">
+        <v>120</v>
+      </c>
+      <c r="S10" s="5">
+        <v>6</v>
+      </c>
+      <c r="T10" s="5">
+        <v>720</v>
+      </c>
+      <c r="Z10" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA10" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB10" s="18">
+        <v>95</v>
+      </c>
+      <c r="AC10" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="17" t="str">
+        <f t="shared" si="0"/>
+        <v>A+</v>
+      </c>
+      <c r="AE10" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF10" s="17" t="str">
+        <f>IFERROR(Table1[[#This Row],[marks]]/Table1[[#This Row],[Column1]],"False")</f>
+        <v>False</v>
+      </c>
+      <c r="AG10" s="17">
+        <f>LEN(Table1[[#This Row],[st. gmails]])</f>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="1">
-        <v>44</v>
-      </c>
-      <c r="F11" s="12">
-        <v>46082</v>
-      </c>
-      <c r="G11" s="11">
-        <v>205</v>
-      </c>
-      <c r="K11">
-        <f>I9+I12</f>
-        <v>600</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>56</v>
+      <c r="C11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1">
-        <v>15</v>
-      </c>
-      <c r="F12" s="12">
-        <v>46113</v>
-      </c>
-      <c r="G12" s="11">
-        <v>207.1</v>
+        <v>30</v>
+      </c>
+      <c r="F12" s="23">
+        <v>46023</v>
+      </c>
+      <c r="G12" s="5">
+        <v>205</v>
       </c>
       <c r="I12">
-        <v>400</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>51</v>
-      </c>
-      <c r="R12" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>60</v>
+        <v>200</v>
+      </c>
+      <c r="Q12">
+        <f>COUNTIF(Q5:Q10,"Fruit")</f>
+        <v>3</v>
+      </c>
+      <c r="R12">
+        <f>SUMIF(Q5:Q10,"Fruit",S5:S10)</f>
+        <v>10</v>
+      </c>
+      <c r="AA12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB12" s="15" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
-      <c r="C13" s="8" t="s">
-        <v>29</v>
+      <c r="C13" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="D13" s="1">
         <v>45</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="23">
+        <v>46054</v>
+      </c>
+      <c r="G13" s="5">
+        <v>206.7</v>
+      </c>
+      <c r="Q13">
+        <f>COUNTIFS(P5:P10,"Frozen",Q5:Q10,"vegetable")</f>
+        <v>2</v>
+      </c>
+      <c r="R13">
+        <f>SUMIFS(S5:S10,P5:P10,"Frozen",Q5:Q10,"Fruit")</f>
+        <v>8</v>
+      </c>
+      <c r="AA13" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB13">
+        <f>VLOOKUP(AA13,Table1[],3,0)</f>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>44</v>
+      </c>
+      <c r="F14" s="23">
+        <v>46082</v>
+      </c>
+      <c r="G14" s="5">
+        <v>205</v>
+      </c>
+      <c r="K14">
+        <f>I12+I15</f>
+        <v>600</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="1">
+        <v>15</v>
+      </c>
+      <c r="F15" s="23">
+        <v>46113</v>
+      </c>
+      <c r="G15" s="5">
+        <v>207.1</v>
+      </c>
+      <c r="I15">
+        <v>400</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>51</v>
+      </c>
+      <c r="R15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="1">
+        <v>45</v>
+      </c>
+      <c r="F16" s="23">
         <v>46143</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G16" s="5">
         <v>208.1</v>
       </c>
-      <c r="Q13" s="5" t="s">
+      <c r="Q16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="R13" s="5" t="s">
+      <c r="R16" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="F14" s="12">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="F17" s="23">
         <v>46174</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G17" s="5">
         <v>207.9</v>
       </c>
-      <c r="K14">
-        <f>I9*5</f>
+      <c r="K17">
+        <f>I12*5</f>
         <v>1000</v>
       </c>
-      <c r="Q14" s="5" t="s">
+      <c r="Q17" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="X14" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="F15" s="12">
-        <v>46204</v>
-      </c>
-      <c r="G15" s="11">
-        <v>208.2</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="K16">
-        <f>I12*6</f>
-        <v>2400</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="I17">
-        <v>1000</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="R17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="X17" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="F18" s="23">
+        <v>46204</v>
+      </c>
+      <c r="G18" s="5">
+        <v>208.2</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="K19">
+        <f>I15*6</f>
+        <v>2400</v>
+      </c>
+      <c r="Q19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="R19" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="C20" s="24"/>
+      <c r="I20">
+        <v>1000</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA20" t="s">
         <v>77</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AB20" t="s">
         <v>78</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AC20" t="s">
         <v>79</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AD20" t="s">
         <v>80</v>
       </c>
-      <c r="AE17" t="s">
+      <c r="AE20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="Q18" s="5" t="s">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="R18" s="5" t="s">
+      <c r="R21" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AA18" s="23" t="s">
+      <c r="AA21" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="AB18" s="22" t="s">
+      <c r="AB21" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="AC18" s="22">
+      <c r="AC21" s="20">
         <v>9</v>
       </c>
-      <c r="AD18" s="22">
+      <c r="AD21" s="20">
         <v>250</v>
       </c>
-      <c r="AE18" s="22">
+      <c r="AE21" s="20">
         <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
         <v>259</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="AA19" s="23" t="s">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AA22" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="AB19" s="22" t="s">
+      <c r="AB22" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="AC19" s="22">
+      <c r="AC22" s="20">
         <v>7</v>
       </c>
-      <c r="AD19" s="22">
+      <c r="AD22" s="20">
         <v>50</v>
       </c>
-      <c r="AE19" s="22">
+      <c r="AE22" s="20">
         <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="K20">
-        <f>I17+55</f>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="K23">
+        <f>I20+55</f>
         <v>1055</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="Q23" t="s">
         <v>42</v>
       </c>
-      <c r="R20" t="s">
+      <c r="R23" t="s">
         <v>46</v>
       </c>
-      <c r="AA20" s="23" t="s">
+      <c r="AA23" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="AB20" s="22" t="s">
+      <c r="AB23" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="AC20" s="22">
+      <c r="AC23" s="20">
         <v>8.5</v>
       </c>
-      <c r="AD20" s="22">
+      <c r="AD23" s="20">
         <v>80</v>
       </c>
-      <c r="AE20" s="22">
+      <c r="AE23" s="20">
         <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
         <v>88.5</v>
       </c>
-      <c r="AH20" s="7"/>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="AA21" s="23" t="s">
+      <c r="AH23" s="7"/>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AA24" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="AB21" s="22" t="s">
+      <c r="AB24" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="AC21" s="22">
+      <c r="AC24" s="20">
         <v>7</v>
       </c>
-      <c r="AD21" s="22">
+      <c r="AD24" s="20">
         <v>700</v>
       </c>
-      <c r="AE21" s="22">
+      <c r="AE24" s="20">
         <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
         <v>707</v>
       </c>
-      <c r="AH21" s="7"/>
-    </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="Q22">
-        <f>SUMIFS(T2:T7,Q13:Q18,Q20,P2:P7,R20)</f>
+      <c r="AH24" s="7"/>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="Q25">
+        <f>SUMIFS(T5:T10,Q16:Q21,Q23,P5:P10,R23)</f>
         <v>300</v>
       </c>
-      <c r="AA22" s="23" t="s">
+      <c r="AA25" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="AB22" s="22" t="s">
+      <c r="AB25" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="AC22" s="22">
+      <c r="AC25" s="20">
         <v>4</v>
       </c>
-      <c r="AD22" s="22">
+      <c r="AD25" s="20">
         <v>100</v>
       </c>
-      <c r="AE22" s="22">
+      <c r="AE25" s="20">
         <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
         <v>104</v>
       </c>
-      <c r="AH22" s="7"/>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA23" s="23" t="s">
+      <c r="AH25" s="7"/>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="AA26" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="AB23" s="22" t="s">
+      <c r="AB26" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="AC23" s="22">
+      <c r="AC26" s="20">
         <v>6</v>
       </c>
-      <c r="AD23" s="22">
+      <c r="AD26" s="20">
         <v>400</v>
       </c>
-      <c r="AE23" s="22">
+      <c r="AE26" s="20">
         <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
         <v>406</v>
       </c>
-      <c r="AH23" s="7"/>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="11">
-        <v>40</v>
-      </c>
-      <c r="E24" s="11">
-        <v>2</v>
-      </c>
-      <c r="F24" s="11">
-        <v>80</v>
-      </c>
-      <c r="AA24" s="23" t="s">
+      <c r="AH26" s="7"/>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="AA27" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="AB24" s="22" t="s">
+      <c r="AB27" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="AC24" s="22">
+      <c r="AC27" s="20">
         <v>10</v>
       </c>
-      <c r="AD24" s="22">
+      <c r="AD27" s="20">
         <v>1000</v>
       </c>
-      <c r="AE24" s="22">
+      <c r="AE27" s="20">
         <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
         <v>1010</v>
       </c>
-      <c r="AH24" s="7"/>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="11">
-        <v>120</v>
-      </c>
-      <c r="E25" s="11">
-        <v>2</v>
-      </c>
-      <c r="F25" s="11">
-        <v>240</v>
-      </c>
-      <c r="J25">
+      <c r="AH27" s="7"/>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="J28">
         <v>200</v>
       </c>
-      <c r="AA25" s="23" t="s">
+      <c r="AA28" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="AB25" s="22" t="s">
+      <c r="AB28" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="AC25" s="22">
+      <c r="AC28" s="20">
         <v>6</v>
       </c>
-      <c r="AD25" s="22">
+      <c r="AD28" s="20">
         <v>50</v>
       </c>
-      <c r="AE25" s="22">
+      <c r="AE28" s="20">
         <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
         <v>56</v>
       </c>
-      <c r="AH25" s="7"/>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="11">
-        <v>60</v>
-      </c>
-      <c r="E26" s="11">
-        <v>4</v>
-      </c>
-      <c r="F26" s="11">
-        <v>240</v>
-      </c>
-      <c r="L26">
-        <f>J25+J27</f>
+      <c r="AH28" s="7"/>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="L29">
+        <f>J28+J30</f>
         <v>500</v>
       </c>
-      <c r="AA26" s="23" t="s">
+      <c r="AA29" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="AB26" s="22" t="s">
+      <c r="AB29" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="AC26" s="22">
+      <c r="AC29" s="20">
         <v>9</v>
       </c>
-      <c r="AD26" s="22">
+      <c r="AD29" s="20">
         <v>70</v>
       </c>
-      <c r="AE26" s="22">
+      <c r="AE29" s="20">
         <f>Table8[[#This Row],[rank]]+Table8[[#This Row],[value]]</f>
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="11">
-        <v>100</v>
-      </c>
-      <c r="E27" s="11">
-        <v>3</v>
-      </c>
-      <c r="F27" s="11">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="J30">
         <v>300</v>
       </c>
-      <c r="J27">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="11">
-        <v>120</v>
-      </c>
-      <c r="E28" s="11">
-        <v>6</v>
-      </c>
-      <c r="F28" s="11">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="11">
-        <v>25</v>
-      </c>
-      <c r="E29" s="11">
-        <v>2</v>
-      </c>
-      <c r="F29" s="11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
     </row>
   </sheetData>
+  <autoFilter ref="O4:T10" xr:uid="{6FC74FB1-AD57-4850-AA87-E06A6A7A96BD}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="O5:T10">
+      <sortCondition ref="S4:S10"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="A2:XFD2"/>
+  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D8:D13">
+  <conditionalFormatting sqref="D11:D16">
     <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
@@ -3510,7 +4996,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB27:AC1048576 AB1:AC8 AB10:AC14 AC9">
+  <conditionalFormatting sqref="AB30:AC1048576 AB4:AC11 AB13:AC17 AC12">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -3524,7 +5010,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE18:AE26">
+  <conditionalFormatting sqref="AE21:AE29">
     <cfRule type="iconSet" priority="1">
       <iconSet iconSet="5Rating">
         <cfvo type="percent" val="0"/>
@@ -3536,26 +5022,26 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q20" xr:uid="{179EE944-FFB1-4A7D-8AAA-099D5A8C61C5}">
-      <formula1>$O$2:$O$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q23" xr:uid="{179EE944-FFB1-4A7D-8AAA-099D5A8C61C5}">
+      <formula1>$O$5:$O$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R13:R18 R20" xr:uid="{994FC5CE-974B-47DC-B8AC-D273DD4BE681}">
-      <formula1>$P$2:$P$7</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R16:R21 R23" xr:uid="{994FC5CE-974B-47DC-B8AC-D273DD4BE681}">
+      <formula1>$P$5:$P$10</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{8CDFE076-B84D-47F7-81DC-EBE01424DE7D}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{37DF5225-85FB-4F03-81A8-4A159C453842}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{450BF1C8-AF3C-42FA-A402-88E9E5A8AD6E}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{D09DE00B-C751-41DE-9407-23E1A969194B}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{CE0B6BFB-416D-4DC4-89A9-32AEA3FCD8B9}"/>
-    <hyperlink ref="AE2" r:id="rId6" xr:uid="{8BCC57DF-F199-48BD-B9B2-36A163AC2B7E}"/>
-    <hyperlink ref="AE3" r:id="rId7" xr:uid="{C363DF98-B913-4F52-8D61-E4E2CEE8989F}"/>
-    <hyperlink ref="AE4" r:id="rId8" xr:uid="{D6B9E294-D4A0-4D86-BF3C-EB5812A8A18A}"/>
-    <hyperlink ref="AE5" r:id="rId9" xr:uid="{5E3054B8-9D43-4564-810F-75FDBE0DDE5C}"/>
-    <hyperlink ref="AE6" r:id="rId10" xr:uid="{20AB87D2-6B90-4AE2-92AD-B1505A6C243F}"/>
-    <hyperlink ref="AE7" r:id="rId11" xr:uid="{BA487083-1955-4B5F-A7AA-75CA81171D32}"/>
-    <hyperlink ref="X14" r:id="rId12" xr:uid="{257603B7-9B4A-4504-83A8-73CCA40D8EE7}"/>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{8CDFE076-B84D-47F7-81DC-EBE01424DE7D}"/>
+    <hyperlink ref="G6" r:id="rId2" xr:uid="{37DF5225-85FB-4F03-81A8-4A159C453842}"/>
+    <hyperlink ref="G7" r:id="rId3" xr:uid="{450BF1C8-AF3C-42FA-A402-88E9E5A8AD6E}"/>
+    <hyperlink ref="G8" r:id="rId4" xr:uid="{D09DE00B-C751-41DE-9407-23E1A969194B}"/>
+    <hyperlink ref="G9" r:id="rId5" xr:uid="{CE0B6BFB-416D-4DC4-89A9-32AEA3FCD8B9}"/>
+    <hyperlink ref="AE5" r:id="rId6" xr:uid="{8BCC57DF-F199-48BD-B9B2-36A163AC2B7E}"/>
+    <hyperlink ref="AE6" r:id="rId7" xr:uid="{C363DF98-B913-4F52-8D61-E4E2CEE8989F}"/>
+    <hyperlink ref="AE7" r:id="rId8" xr:uid="{D6B9E294-D4A0-4D86-BF3C-EB5812A8A18A}"/>
+    <hyperlink ref="AE8" r:id="rId9" xr:uid="{5E3054B8-9D43-4564-810F-75FDBE0DDE5C}"/>
+    <hyperlink ref="AE9" r:id="rId10" xr:uid="{20AB87D2-6B90-4AE2-92AD-B1505A6C243F}"/>
+    <hyperlink ref="AE10" r:id="rId11" xr:uid="{BA487083-1955-4B5F-A7AA-75CA81171D32}"/>
+    <hyperlink ref="X17" r:id="rId12" xr:uid="{257603B7-9B4A-4504-83A8-73CCA40D8EE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId13"/>
@@ -3578,7 +5064,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D8:D13</xm:sqref>
+          <xm:sqref>D11:D16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{D112B2C1-F653-4E25-A221-59F742710B7E}">
@@ -3591,10 +5077,465 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AB27:AC1048576 AB1:AC8 AB10:AC14 AC9</xm:sqref>
+          <xm:sqref>AB30:AC1048576 AB4:AC11 AB13:AC17 AC12</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB9D73F-6F60-4BE9-880B-44F6295A60F0}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="25">
+        <v>55</v>
+      </c>
+      <c r="C2" s="25">
+        <f ca="1">RANDBETWEEN(50,66)</f>
+        <v>66</v>
+      </c>
+      <c r="D2" s="25">
+        <f ca="1">RANDBETWEEN(55,66)</f>
+        <v>59</v>
+      </c>
+      <c r="E2" s="27">
+        <f t="shared" ref="E2:E8" ca="1" si="0">RANDBETWEEN(50,66)</f>
+        <v>53</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="25">
+        <v>62</v>
+      </c>
+      <c r="C3" s="25">
+        <f t="shared" ref="C3:C8" ca="1" si="1">RANDBETWEEN(50,66)</f>
+        <v>51</v>
+      </c>
+      <c r="D3" s="25">
+        <f t="shared" ref="D3:D8" ca="1" si="2">RANDBETWEEN(55,66)</f>
+        <v>60</v>
+      </c>
+      <c r="E3" s="27">
+        <f t="shared" ca="1" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="25">
+        <v>50</v>
+      </c>
+      <c r="C4" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="D4" s="25">
+        <f t="shared" ca="1" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="E4" s="27">
+        <f t="shared" ca="1" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="25"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="25">
+        <v>52</v>
+      </c>
+      <c r="C5" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="D5" s="25">
+        <f t="shared" ca="1" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="E5" s="27">
+        <f t="shared" ca="1" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="25"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="25">
+        <v>55</v>
+      </c>
+      <c r="C6" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="D6" s="25">
+        <f t="shared" ca="1" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="E6" s="27">
+        <f t="shared" ca="1" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" s="25"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="25">
+        <v>54</v>
+      </c>
+      <c r="C7" s="25">
+        <f t="shared" ca="1" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="D7" s="25">
+        <f t="shared" ca="1" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="E7" s="27">
+        <f t="shared" ca="1" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="29">
+        <v>56</v>
+      </c>
+      <c r="C8" s="29">
+        <f t="shared" ca="1" si="1"/>
+        <v>66</v>
+      </c>
+      <c r="D8" s="29">
+        <f t="shared" ca="1" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="E8" s="30">
+        <f t="shared" ca="1" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="29"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <f ca="1">SUMIF(D2:D8,64,E2:E8)</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <f ca="1">SUMIFS(E2:E8,B2:B8,50)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" t="str">
+        <f>_xlfn.XLOOKUP(B8,maths,student_name)</f>
+        <v>roman</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <f>MATCH(A12,student_name,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="str">
+        <f>INDEX(student_name,4)</f>
+        <v>raj</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <f>VLOOKUP(A12,Table2[#All],2)</f>
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G8" xr:uid="{E6410891-7444-4BF1-B7B4-03F6C9E22C50}">
+      <formula1>80</formula1>
+      <formula2>88</formula2>
+    </dataValidation>
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{A3F16F2C-D135-4F24-9CD7-6691037A798A}">
+      <formula1>80</formula1>
+      <formula2>88</formula2>
+    </dataValidation>
+    <dataValidation type="whole" errorStyle="information" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3" xr:uid="{7FB397A4-004D-4103-BF94-C06BAB8B8D17}">
+      <formula1>80</formula1>
+      <formula2>88</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="stop sujal" sqref="G4" xr:uid="{18A5BDCD-FDB3-4829-96E5-51EF3D194E82}">
+      <formula1>80</formula1>
+      <formula2>88</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{3CDCEBA4-4316-4C8D-AF88-C77C1274C046}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{0E283A4E-2D31-4D1E-8018-8784D140A7AE}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{00A6A04A-4C73-42F9-9A73-74BA05204A45}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{C221CDA5-5711-400C-9955-AC25F81B33D8}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{156F7A13-5437-424D-9CAD-C27F3336597A}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{F559ED4F-FEFE-459F-A73C-AFC7A86EF6C0}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{E6A873A7-0664-4568-B1D1-6B4398BE64B0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId8"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE4F0E29-7FDB-4CC3-9BB6-9F3D7D1478D3}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>22</v>
+      </c>
+      <c r="B2" s="25">
+        <v>33</v>
+      </c>
+      <c r="C2" s="25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="39"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB0ECD7-39B1-4B1D-84D6-92D390A17790}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>66</v>
+      </c>
+      <c r="B2" s="25">
+        <v>55</v>
+      </c>
+      <c r="C2" s="25">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32CCBD4-07A2-45B7-8425-D2EE7667E726}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
+        <v>99</v>
+      </c>
+      <c r="B2" s="25">
+        <v>22</v>
+      </c>
+      <c r="C2" s="25">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{776D990D-825E-4B18-92B4-577FAB4651EE}">
+  <dimension ref="A2:C5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <f>Sheet3!$A$2</f>
+        <v>22</v>
+      </c>
+      <c r="B2">
+        <f>Sheet3!$B$2</f>
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <f>Sheet3!$C$2</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>Sheet4!$A$2</f>
+        <v>66</v>
+      </c>
+      <c r="B3">
+        <f>Sheet4!$B$2</f>
+        <v>55</v>
+      </c>
+      <c r="C3">
+        <f>Sheet4!$C$2</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f>Sheet5!$A$2</f>
+        <v>99</v>
+      </c>
+      <c r="B4">
+        <f>Sheet5!$B$2</f>
+        <v>22</v>
+      </c>
+      <c r="C4">
+        <f>Sheet5!$C$2</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f>SUM(A2:A4)</f>
+        <v>187</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v>110</v>
+      </c>
+      <c r="C5">
+        <f>SUM(C2:C4)</f>
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate link="1">
+    <dataRefs count="3">
+      <dataRef ref="A1:C2" sheet="Sheet3"/>
+      <dataRef ref="A1:C2" sheet="Sheet4"/>
+      <dataRef ref="A1:C2" sheet="Sheet5"/>
+    </dataRefs>
+  </dataConsolidate>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>